--- a/app/www/profiles/profile-Wine-zgpr-500.xlsx
+++ b/app/www/profiles/profile-Wine-zgpr-500.xlsx
@@ -5,22 +5,22 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workdir\Metabolomic\NMRProcFlow\git\RnmrQuant1D\RnmrQuant1D_UI\www\profiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workdir\Metabolomic\WAP-NMR\Manips\URO_RMN_500\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B433CD-F555-4463-80C9-0264989AE557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E823528-3DFF-460A-B483-4E6D8883F4DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="2595" windowWidth="21600" windowHeight="11235" xr2:uid="{524AC9D9-352A-4B49-9285-9FC9260D37F8}"/>
+    <workbookView xWindow="1755" yWindow="810" windowWidth="22410" windowHeight="12780" xr2:uid="{524AC9D9-352A-4B49-9285-9FC9260D37F8}"/>
   </bookViews>
   <sheets>
     <sheet name="profile-zgpr-400" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="76">
   <si>
     <t>#=====================================================================</t>
   </si>
@@ -214,9 +214,6 @@
     <t>r5</t>
   </si>
   <si>
-    <t>0,1.2,0.55</t>
-  </si>
-  <si>
     <t>choline</t>
   </si>
   <si>
@@ -232,19 +229,25 @@
     <t>0.97,1.06,1.046,s</t>
   </si>
   <si>
-    <t>1.399,1.405,0,1.2,0.1</t>
-  </si>
-  <si>
     <t>3.272,3.284,3.279,s</t>
   </si>
   <si>
     <t>3.34,3.36,3.35,s</t>
   </si>
   <si>
-    <t>3.356,3.362,0,2,0.5</t>
-  </si>
-  <si>
     <t>1.12,1.128,1.123,s</t>
+  </si>
+  <si>
+    <t>3.359,3.365,0,6,0.5,120</t>
+  </si>
+  <si>
+    <t>1.371,1.422,1.4,d</t>
+  </si>
+  <si>
+    <t>1.393,1.406,0,6,0.15,120</t>
+  </si>
+  <si>
+    <t>0,5,0.55</t>
   </si>
 </sst>
 </file>
@@ -1124,7 +1127,7 @@
     <col min="2" max="2" width="14.7109375" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="23.7109375" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" customWidth="1"/>
+    <col min="6" max="6" width="24.5703125" customWidth="1"/>
     <col min="7" max="7" width="17.7109375" customWidth="1"/>
     <col min="9" max="9" width="11.28515625" customWidth="1"/>
   </cols>
@@ -1286,7 +1289,7 @@
         <v>31</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1300,10 +1303,10 @@
         <v>2</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1375,7 +1378,7 @@
         <v>42</v>
       </c>
       <c r="B37" s="5">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="C37" s="5">
         <v>1.44</v>
@@ -1416,7 +1419,7 @@
         <v>0</v>
       </c>
       <c r="E38" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F38" s="4">
         <v>50</v>
@@ -1521,7 +1524,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H43" s="4">
         <v>6</v>
@@ -1556,7 +1559,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H44" s="4">
         <v>6</v>
@@ -1587,11 +1590,11 @@
       <c r="E45" s="4">
         <v>7</v>
       </c>
-      <c r="F45" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="G45" s="4">
-        <v>0</v>
+      <c r="F45" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="H45" s="4">
         <v>6</v>
@@ -1611,13 +1614,13 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>54</v>
       </c>
       <c r="D46" s="4">
-        <v>3.18</v>
+        <v>3.1789999999999998</v>
       </c>
       <c r="E46" s="4">
         <v>3.1949999999999998</v>
@@ -1655,13 +1658,13 @@
         <v>3.2605</v>
       </c>
       <c r="E47" s="4">
-        <v>9.25</v>
+        <v>9.4</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H47" s="4">
         <v>6</v>
@@ -1696,7 +1699,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H48" s="4">
         <v>6</v>
@@ -1722,16 +1725,16 @@
         <v>63</v>
       </c>
       <c r="D49" s="4">
-        <v>3.359</v>
+        <v>3.3620000000000001</v>
       </c>
       <c r="E49" s="4">
         <v>6.6</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G49" s="4">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="H49" s="4">
         <v>6</v>
@@ -1763,7 +1766,7 @@
         <v>3.5779999999999998</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G50" s="4">
         <v>0</v>
@@ -1863,7 +1866,7 @@
         <v>43</v>
       </c>
       <c r="B60" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C60">
         <v>104.1708</v>
